--- a/Калькулятор_экономики_игры.xlsx
+++ b/Калькулятор_экономики_игры.xlsx
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1930.67</v>
+        <v>750.8099999999999</v>
       </c>
     </row>
     <row r="7">
@@ -647,7 +647,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.14</v>
+        <v>0.36</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0.28</v>
+        <v>0.73</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>0.44</v>
+        <v>1.12</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>0.59</v>
+        <v>1.53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>25</v>
       </c>
       <c r="E7" t="n">
-        <v>0.76</v>
+        <v>1.95</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>30</v>
       </c>
       <c r="E8" t="n">
-        <v>0.93</v>
+        <v>2.4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>35</v>
       </c>
       <c r="E9" t="n">
-        <v>1.11</v>
+        <v>2.86</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>40</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3</v>
+        <v>3.34</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>45</v>
       </c>
       <c r="E11" t="n">
-        <v>1.49</v>
+        <v>3.84</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>53</v>
       </c>
       <c r="E12" t="n">
-        <v>1.69</v>
+        <v>4.35</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>58</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9</v>
+        <v>4.88</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>63</v>
       </c>
       <c r="E14" t="n">
-        <v>2.11</v>
+        <v>5.43</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>68</v>
       </c>
       <c r="E15" t="n">
-        <v>2.33</v>
+        <v>6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>73</v>
       </c>
       <c r="E16" t="n">
-        <v>2.56</v>
+        <v>6.59</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>78</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8</v>
+        <v>7.19</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>83</v>
       </c>
       <c r="E18" t="n">
-        <v>3.04</v>
+        <v>7.81</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>88</v>
       </c>
       <c r="E19" t="n">
-        <v>3.29</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>93</v>
       </c>
       <c r="E20" t="n">
-        <v>3.54</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>98</v>
       </c>
       <c r="E21" t="n">
-        <v>3.81</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>108</v>
       </c>
       <c r="E22" t="n">
-        <v>4.07</v>
+        <v>10.48</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>113</v>
       </c>
       <c r="E23" t="n">
-        <v>4.36</v>
+        <v>11.21</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>118</v>
       </c>
       <c r="E24" t="n">
-        <v>4.65</v>
+        <v>11.95</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>123</v>
       </c>
       <c r="E25" t="n">
-        <v>4.94</v>
+        <v>12.72</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>128</v>
       </c>
       <c r="E26" t="n">
-        <v>5.25</v>
+        <v>13.5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>133</v>
       </c>
       <c r="E27" t="n">
-        <v>5.56</v>
+        <v>14.3</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>138</v>
       </c>
       <c r="E28" t="n">
-        <v>5.88</v>
+        <v>15.11</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>143</v>
       </c>
       <c r="E29" t="n">
-        <v>6.2</v>
+        <v>15.95</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>148</v>
       </c>
       <c r="E30" t="n">
-        <v>6.53</v>
+        <v>16.8</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>153</v>
       </c>
       <c r="E31" t="n">
-        <v>6.87</v>
+        <v>17.67</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>163</v>
       </c>
       <c r="E32" t="n">
-        <v>7.22</v>
+        <v>18.56</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>168</v>
       </c>
       <c r="E33" t="n">
-        <v>7.57</v>
+        <v>19.46</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>173</v>
       </c>
       <c r="E34" t="n">
-        <v>7.93</v>
+        <v>20.39</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>178</v>
       </c>
       <c r="E35" t="n">
-        <v>8.289999999999999</v>
+        <v>21.33</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>183</v>
       </c>
       <c r="E36" t="n">
-        <v>8.67</v>
+        <v>22.29</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>188</v>
       </c>
       <c r="E37" t="n">
-        <v>9.050000000000001</v>
+        <v>23.26</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>193</v>
       </c>
       <c r="E38" t="n">
-        <v>9.43</v>
+        <v>24.26</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>198</v>
       </c>
       <c r="E39" t="n">
-        <v>9.83</v>
+        <v>25.27</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>203</v>
       </c>
       <c r="E40" t="n">
-        <v>10.23</v>
+        <v>26.3</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>208</v>
       </c>
       <c r="E41" t="n">
-        <v>10.64</v>
+        <v>27.35</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>220</v>
       </c>
       <c r="E42" t="n">
-        <v>11.05</v>
+        <v>28.41</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>225</v>
       </c>
       <c r="E43" t="n">
-        <v>11.47</v>
+        <v>29.5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>230</v>
       </c>
       <c r="E44" t="n">
-        <v>11.9</v>
+        <v>30.6</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>235</v>
       </c>
       <c r="E45" t="n">
-        <v>12.33</v>
+        <v>31.72</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>240</v>
       </c>
       <c r="E46" t="n">
-        <v>12.78</v>
+        <v>32.85</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>245</v>
       </c>
       <c r="E47" t="n">
-        <v>13.23</v>
+        <v>34.01</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>250</v>
       </c>
       <c r="E48" t="n">
-        <v>13.68</v>
+        <v>35.18</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>255</v>
       </c>
       <c r="E49" t="n">
-        <v>14.14</v>
+        <v>36.37</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>260</v>
       </c>
       <c r="E50" t="n">
-        <v>14.61</v>
+        <v>37.58</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>265</v>
       </c>
       <c r="E51" t="n">
-        <v>15.09</v>
+        <v>38.8</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>278</v>
       </c>
       <c r="E52" t="n">
-        <v>15.57</v>
+        <v>40.05</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>283</v>
       </c>
       <c r="E53" t="n">
-        <v>16.07</v>
+        <v>41.33</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>288</v>
       </c>
       <c r="E54" t="n">
-        <v>16.59</v>
+        <v>42.65</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>293</v>
       </c>
       <c r="E55" t="n">
-        <v>17.11</v>
+        <v>44</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>298</v>
       </c>
       <c r="E56" t="n">
-        <v>17.65</v>
+        <v>45.38</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>303</v>
       </c>
       <c r="E57" t="n">
-        <v>18.2</v>
+        <v>46.79</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>308</v>
       </c>
       <c r="E58" t="n">
-        <v>18.76</v>
+        <v>48.24</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>313</v>
       </c>
       <c r="E59" t="n">
-        <v>19.33</v>
+        <v>49.71</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>318</v>
       </c>
       <c r="E60" t="n">
-        <v>19.92</v>
+        <v>51.22</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>323</v>
       </c>
       <c r="E61" t="n">
-        <v>20.51</v>
+        <v>52.75</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>336</v>
       </c>
       <c r="E62" t="n">
-        <v>21.12</v>
+        <v>54.32</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>341</v>
       </c>
       <c r="E63" t="n">
-        <v>21.75</v>
+        <v>55.92</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>346</v>
       </c>
       <c r="E64" t="n">
-        <v>22.38</v>
+        <v>57.55</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>351</v>
       </c>
       <c r="E65" t="n">
-        <v>23.02</v>
+        <v>59.21</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>356</v>
       </c>
       <c r="E66" t="n">
-        <v>23.68</v>
+        <v>60.9</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>361</v>
       </c>
       <c r="E67" t="n">
-        <v>24.35</v>
+        <v>62.62</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>366</v>
       </c>
       <c r="E68" t="n">
-        <v>25.03</v>
+        <v>64.37</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>371</v>
       </c>
       <c r="E69" t="n">
-        <v>25.73</v>
+        <v>66.16</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>376</v>
       </c>
       <c r="E70" t="n">
-        <v>26.43</v>
+        <v>67.98</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>381</v>
       </c>
       <c r="E71" t="n">
-        <v>27.15</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>396</v>
       </c>
       <c r="E72" t="n">
-        <v>27.88</v>
+        <v>71.7</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>401</v>
       </c>
       <c r="E73" t="n">
-        <v>28.63</v>
+        <v>73.61</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>406</v>
       </c>
       <c r="E74" t="n">
-        <v>29.38</v>
+        <v>75.55</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>411</v>
       </c>
       <c r="E75" t="n">
-        <v>30.15</v>
+        <v>77.52</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>416</v>
       </c>
       <c r="E76" t="n">
-        <v>30.93</v>
+        <v>79.52</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>421</v>
       </c>
       <c r="E77" t="n">
-        <v>31.72</v>
+        <v>81.56</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>426</v>
       </c>
       <c r="E78" t="n">
-        <v>32.52</v>
+        <v>83.62</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>431</v>
       </c>
       <c r="E79" t="n">
-        <v>33.33</v>
+        <v>85.72</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>436</v>
       </c>
       <c r="E80" t="n">
-        <v>34.16</v>
+        <v>87.84</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>441</v>
       </c>
       <c r="E81" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
